--- a/club_selector.xlsx
+++ b/club_selector.xlsx
@@ -465,7 +465,7 @@
         <v>103.9</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -530,14 +530,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pw</t>
+          <t>gw</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.75</v>
+        <v>122.5</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -584,14 +584,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9i</t>
+          <t>8i</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>138.5</v>
+        <v>138.9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
         <v>153.2</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -771,7 +771,7 @@
         <v>188.2</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -836,7 +836,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>3w</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -879,7 +879,7 @@
         <v>217.7</v>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/club_selector.xlsx
+++ b/club_selector.xlsx
@@ -458,14 +458,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gw</t>
+          <t>pw</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>103.9</v>
+        <v>103.5</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -530,14 +530,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gw</t>
+          <t>9i</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>122.5</v>
+        <v>123.6</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -548,14 +548,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9i</t>
+          <t>6i</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>129.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         <v>153.2</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -836,14 +836,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3w</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>208.45</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/club_selector.xlsx
+++ b/club_selector.xlsx
@@ -476,11 +476,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lw</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109.4</v>
+        <v>108.4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>123.6</v>
+        <v>123.05</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         <v>138.9</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -602,14 +602,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6i</t>
+          <t>7i</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>144.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -645,7 +645,7 @@
         <v>153.2</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>175</v>
+        <v>174.45</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -735,7 +735,7 @@
         <v>178.3</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -764,14 +764,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4i</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>188.2</v>
+        <v>189.3</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -800,14 +800,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>198</v>
+        <v>197.25</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -825,7 +825,7 @@
         <v>204.6</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>208.45</v>
+        <v>208.7</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>214.4</v>
+        <v>212.75</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -879,7 +879,7 @@
         <v>217.7</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
